--- a/StructureDefinition-SEEHDSLMLaboratoryOrderOutcomeV31.xlsx
+++ b/StructureDefinition-SEEHDSLMLaboratoryOrderOutcomeV31.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMLaboratoryOrderOutcomeV31.xlsx
+++ b/StructureDefinition-SEEHDSLMLaboratoryOrderOutcomeV31.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3990" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3990" uniqueCount="352">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -773,6 +773,10 @@
   </si>
   <si>
     <t>Information om analystjänster som ligger till grund för ett undersökningsresultat</t>
+  </si>
+  <si>
+    <t>getlaboratoryorderoutcome31-analysis-choice:Ett och endast ett av analysisCode och analysisText ska anges {analysisCode.exists() xor analysisText.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>SEEHDSLMLaboratoryOrderOutcomeV31.laboratoryOrderOutcome.laboratoryOrderOutcomeBody.analysis.id</t>
@@ -9187,15 +9191,15 @@
         <v>72</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>81</v>
+        <v>246</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9292,10 +9296,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9394,10 +9398,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9498,10 +9502,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9524,13 +9528,13 @@
         <v>72</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9581,7 +9585,7 @@
         <v>72</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>83</v>
@@ -9598,10 +9602,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9624,13 +9628,13 @@
         <v>72</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9681,7 +9685,7 @@
         <v>72</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>73</v>
@@ -9698,10 +9702,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9727,10 +9731,10 @@
         <v>144</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9781,7 +9785,7 @@
         <v>72</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>73</v>
@@ -9798,10 +9802,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9827,10 +9831,10 @@
         <v>112</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -9881,7 +9885,7 @@
         <v>72</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>73</v>
@@ -9898,10 +9902,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9927,10 +9931,10 @@
         <v>112</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -9981,7 +9985,7 @@
         <v>72</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>73</v>
@@ -9998,10 +10002,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10027,10 +10031,10 @@
         <v>112</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10081,7 +10085,7 @@
         <v>72</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>73</v>
@@ -10098,10 +10102,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10127,10 +10131,10 @@
         <v>112</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10181,7 +10185,7 @@
         <v>72</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>73</v>
@@ -10198,10 +10202,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10227,10 +10231,10 @@
         <v>112</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10281,7 +10285,7 @@
         <v>72</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>73</v>
@@ -10298,10 +10302,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10327,10 +10331,10 @@
         <v>78</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10381,7 +10385,7 @@
         <v>72</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>73</v>
@@ -10398,10 +10402,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10498,10 +10502,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10600,10 +10604,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10704,10 +10708,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10730,13 +10734,13 @@
         <v>72</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -10787,7 +10791,7 @@
         <v>72</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>83</v>
@@ -10804,10 +10808,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10833,10 +10837,10 @@
         <v>78</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -10887,7 +10891,7 @@
         <v>72</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>73</v>
@@ -10904,10 +10908,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11004,10 +11008,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11106,10 +11110,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11210,10 +11214,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11239,10 +11243,10 @@
         <v>112</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -11293,7 +11297,7 @@
         <v>72</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>83</v>
@@ -11310,10 +11314,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11339,10 +11343,10 @@
         <v>112</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -11393,7 +11397,7 @@
         <v>72</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>73</v>
@@ -11410,10 +11414,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11439,7 +11443,7 @@
         <v>122</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M100" t="s" s="2">
         <v>124</v>
@@ -11493,7 +11497,7 @@
         <v>72</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>73</v>
@@ -11510,10 +11514,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11539,10 +11543,10 @@
         <v>189</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -11593,7 +11597,7 @@
         <v>72</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>83</v>
@@ -11610,10 +11614,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11639,10 +11643,10 @@
         <v>112</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -11693,7 +11697,7 @@
         <v>72</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>73</v>
@@ -11710,10 +11714,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11739,10 +11743,10 @@
         <v>112</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -11793,7 +11797,7 @@
         <v>72</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>73</v>
@@ -11810,10 +11814,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -11839,10 +11843,10 @@
         <v>112</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -11893,7 +11897,7 @@
         <v>72</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>73</v>
@@ -11910,10 +11914,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -11939,10 +11943,10 @@
         <v>78</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -11993,7 +11997,7 @@
         <v>72</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>73</v>
@@ -12010,10 +12014,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12110,10 +12114,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12212,10 +12216,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12316,10 +12320,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12345,7 +12349,7 @@
         <v>122</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M109" t="s" s="2">
         <v>124</v>
@@ -12399,7 +12403,7 @@
         <v>72</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>83</v>
@@ -12416,10 +12420,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12445,10 +12449,10 @@
         <v>112</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -12499,7 +12503,7 @@
         <v>72</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>73</v>
@@ -12516,10 +12520,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12545,10 +12549,10 @@
         <v>112</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -12599,7 +12603,7 @@
         <v>72</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>73</v>
@@ -12616,10 +12620,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12645,10 +12649,10 @@
         <v>78</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -12699,7 +12703,7 @@
         <v>72</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>83</v>
@@ -12716,10 +12720,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12816,10 +12820,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -12918,10 +12922,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13022,10 +13026,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13051,10 +13055,10 @@
         <v>112</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -13105,7 +13109,7 @@
         <v>72</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>83</v>
@@ -13122,10 +13126,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13151,10 +13155,10 @@
         <v>112</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -13205,7 +13209,7 @@
         <v>72</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>73</v>
@@ -13222,10 +13226,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13251,10 +13255,10 @@
         <v>78</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -13305,7 +13309,7 @@
         <v>72</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>83</v>
@@ -13322,10 +13326,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13422,10 +13426,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13524,10 +13528,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13628,10 +13632,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13657,10 +13661,10 @@
         <v>112</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -13711,7 +13715,7 @@
         <v>72</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>83</v>
@@ -13728,10 +13732,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -13757,10 +13761,10 @@
         <v>112</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -13811,7 +13815,7 @@
         <v>72</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>73</v>
@@ -13828,10 +13832,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -13857,10 +13861,10 @@
         <v>112</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -13911,7 +13915,7 @@
         <v>72</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>83</v>
@@ -13928,10 +13932,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -13957,10 +13961,10 @@
         <v>112</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -14011,7 +14015,7 @@
         <v>72</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>73</v>
@@ -14028,10 +14032,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14057,10 +14061,10 @@
         <v>112</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -14111,7 +14115,7 @@
         <v>72</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>73</v>

--- a/StructureDefinition-SEEHDSLMLaboratoryOrderOutcomeV31.xlsx
+++ b/StructureDefinition-SEEHDSLMLaboratoryOrderOutcomeV31.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMLaboratoryOrderOutcomeV31.xlsx
+++ b/StructureDefinition-SEEHDSLMLaboratoryOrderOutcomeV31.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
